--- a/OTT_스케쥴표.xlsx
+++ b/OTT_스케쥴표.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seong\OneDrive\바탕 화면\AI 프로젝트\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{79452562-388D-4A7B-A9AB-3C45FEF7F15C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D863014A-FFD4-4B4F-AA2B-4E7ED2632590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5580" yWindow="0" windowWidth="16785" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="개발스케줄표" sheetId="1" r:id="rId1"/>
@@ -98,9 +98,6 @@
     <t>변수 가공 및 피처 생성</t>
   </si>
   <si>
-    <t>머신러닝</t>
-  </si>
-  <si>
     <t>기능1 모델 설계 (해지 위험도 예측)</t>
   </si>
   <si>
@@ -165,6 +162,10 @@
   </si>
   <si>
     <t>최종 점검</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>모델링(ML) 개발</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -173,7 +174,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="m/d"/>
+    <numFmt numFmtId="176" formatCode="m/d"/>
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
@@ -426,10 +427,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -483,39 +484,39 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -828,7 +829,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="27.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="33"/>
@@ -874,7 +875,7 @@
       <c r="AP1" s="33"/>
     </row>
     <row r="2" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="39" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="33"/>
@@ -926,58 +927,58 @@
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="30" t="s">
+      <c r="D4" s="30"/>
+      <c r="E4" s="30"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="30"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="31"/>
-      <c r="L4" s="31"/>
-      <c r="M4" s="31"/>
-      <c r="N4" s="31"/>
-      <c r="O4" s="31"/>
-      <c r="P4" s="31"/>
-      <c r="Q4" s="30" t="s">
+      <c r="K4" s="30"/>
+      <c r="L4" s="30"/>
+      <c r="M4" s="30"/>
+      <c r="N4" s="30"/>
+      <c r="O4" s="30"/>
+      <c r="P4" s="30"/>
+      <c r="Q4" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="R4" s="31"/>
-      <c r="S4" s="31"/>
-      <c r="T4" s="31"/>
-      <c r="U4" s="31"/>
-      <c r="V4" s="31"/>
-      <c r="W4" s="31"/>
-      <c r="X4" s="30" t="s">
+      <c r="R4" s="30"/>
+      <c r="S4" s="30"/>
+      <c r="T4" s="30"/>
+      <c r="U4" s="30"/>
+      <c r="V4" s="30"/>
+      <c r="W4" s="30"/>
+      <c r="X4" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="Y4" s="31"/>
-      <c r="Z4" s="31"/>
-      <c r="AA4" s="31"/>
-      <c r="AB4" s="31"/>
-      <c r="AC4" s="31"/>
-      <c r="AD4" s="31"/>
-      <c r="AE4" s="30" t="s">
+      <c r="Y4" s="30"/>
+      <c r="Z4" s="30"/>
+      <c r="AA4" s="30"/>
+      <c r="AB4" s="30"/>
+      <c r="AC4" s="30"/>
+      <c r="AD4" s="30"/>
+      <c r="AE4" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="AF4" s="31"/>
-      <c r="AG4" s="31"/>
-      <c r="AH4" s="31"/>
-      <c r="AI4" s="31"/>
-      <c r="AJ4" s="31"/>
-      <c r="AK4" s="31"/>
-      <c r="AL4" s="30" t="s">
+      <c r="AF4" s="30"/>
+      <c r="AG4" s="30"/>
+      <c r="AH4" s="30"/>
+      <c r="AI4" s="30"/>
+      <c r="AJ4" s="30"/>
+      <c r="AK4" s="30"/>
+      <c r="AL4" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="AM4" s="31"/>
-      <c r="AN4" s="31"/>
-      <c r="AO4" s="31"/>
-      <c r="AP4" s="31"/>
+      <c r="AM4" s="30"/>
+      <c r="AN4" s="30"/>
+      <c r="AO4" s="30"/>
+      <c r="AP4" s="30"/>
     </row>
     <row r="5" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2"/>
@@ -1104,7 +1105,7 @@
       </c>
     </row>
     <row r="6" spans="1:42" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="39" t="s">
+      <c r="A6" s="35" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="5" t="s">
@@ -1256,7 +1257,7 @@
       <c r="AP8" s="8"/>
     </row>
     <row r="9" spans="1:42" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="37" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="5" t="s">
@@ -1454,11 +1455,11 @@
       <c r="AP12" s="8"/>
     </row>
     <row r="13" spans="1:42" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="26" t="s">
+      <c r="A13" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>22</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
@@ -1508,7 +1509,7 @@
     <row r="14" spans="1:42" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="27"/>
       <c r="B14" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
@@ -1558,7 +1559,7 @@
     <row r="15" spans="1:42" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="27"/>
       <c r="B15" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
@@ -1608,7 +1609,7 @@
     <row r="16" spans="1:42" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="28"/>
       <c r="B16" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
@@ -1656,11 +1657,11 @@
       <c r="AP16" s="8"/>
     </row>
     <row r="17" spans="1:42" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="34" t="s">
+      <c r="A17" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>27</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
@@ -1710,7 +1711,7 @@
     <row r="18" spans="1:42" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="27"/>
       <c r="B18" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
@@ -1760,7 +1761,7 @@
     <row r="19" spans="1:42" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="28"/>
       <c r="B19" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
@@ -1808,11 +1809,11 @@
       <c r="AP19" s="8"/>
     </row>
     <row r="20" spans="1:42" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="35" t="s">
+      <c r="A20" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>30</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>31</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
@@ -1860,7 +1861,7 @@
     <row r="21" spans="1:42" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="27"/>
       <c r="B21" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
@@ -1910,7 +1911,7 @@
     <row r="22" spans="1:42" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="28"/>
       <c r="B22" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
@@ -1956,11 +1957,11 @@
       <c r="AP22" s="8"/>
     </row>
     <row r="23" spans="1:42" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="37" t="s">
+      <c r="A23" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>34</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>35</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
@@ -2008,7 +2009,7 @@
     <row r="24" spans="1:42" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="27"/>
       <c r="B24" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
@@ -2056,7 +2057,7 @@
     <row r="25" spans="1:42" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="28"/>
       <c r="B25" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
@@ -2103,33 +2104,33 @@
     </row>
     <row r="28" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A28" s="18" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B28" s="19"/>
       <c r="C28" s="21"/>
       <c r="D28" s="20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F28" s="22"/>
       <c r="G28" s="20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I28" s="23"/>
       <c r="J28" s="20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L28" s="24"/>
       <c r="M28" s="20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="O28" s="25"/>
       <c r="P28" s="20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:42" x14ac:dyDescent="0.3">
-      <c r="A30" s="36" t="s">
-        <v>42</v>
+      <c r="A30" s="32" t="s">
+        <v>41</v>
       </c>
       <c r="B30" s="33"/>
       <c r="C30" s="33"/>
@@ -2219,6 +2220,9 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A1:AP1"/>
+    <mergeCell ref="X4:AD4"/>
+    <mergeCell ref="A2:AP2"/>
     <mergeCell ref="A17:A19"/>
     <mergeCell ref="Q4:W4"/>
     <mergeCell ref="A20:A22"/>
@@ -2231,9 +2235,6 @@
     <mergeCell ref="A13:A16"/>
     <mergeCell ref="A9:A12"/>
     <mergeCell ref="J4:P4"/>
-    <mergeCell ref="A1:AP1"/>
-    <mergeCell ref="X4:AD4"/>
-    <mergeCell ref="A2:AP2"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
